--- a/Decks/Arabella.xlsx
+++ b/Decks/Arabella.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C178318-9CB8-4044-93B1-89DBE519E4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{230313CA-5192-4F1D-9E0D-431AE6D52AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F75D263A-00FE-40E8-A865-C2160008CFD6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="135">
   <si>
     <t>Função</t>
   </si>
@@ -101,9 +101,6 @@
     <t>Raid Bombardment</t>
   </si>
   <si>
-    <t>Raise the Alarms</t>
-  </si>
-  <si>
     <t>Dragon Fodder</t>
   </si>
   <si>
@@ -275,27 +272,18 @@
     <t>Alabaster Mage</t>
   </si>
   <si>
-    <t>Cabbareti Courtyard</t>
-  </si>
-  <si>
     <t>Celestial Unicorn</t>
   </si>
   <si>
     <t>Chrome Companion</t>
   </si>
   <si>
-    <t>Cursebreaker</t>
-  </si>
-  <si>
     <t>Dawnbringer Cleric</t>
   </si>
   <si>
     <t>Deadly Riposte</t>
   </si>
   <si>
-    <t>Decommision</t>
-  </si>
-  <si>
     <t>Dimension X</t>
   </si>
   <si>
@@ -380,9 +368,6 @@
     <t>Secluded Steppe</t>
   </si>
   <si>
-    <t>Field's of Strife</t>
-  </si>
-  <si>
     <t>Underfoot Underdogs</t>
   </si>
   <si>
@@ -441,6 +426,21 @@
   </si>
   <si>
     <t>Alpine Meadow</t>
+  </si>
+  <si>
+    <t>Cursebreak</t>
+  </si>
+  <si>
+    <t>Decommission</t>
+  </si>
+  <si>
+    <t>Fields of Strife</t>
+  </si>
+  <si>
+    <t>Raise the Alarm</t>
+  </si>
+  <si>
+    <t>Cabaretti Courtyard</t>
   </si>
 </sst>
 </file>
@@ -884,11 +884,13 @@
       </c>
       <c r="B3" s="5" t="b">
         <f t="shared" ref="B3:B64" si="0">C3&lt;&gt;D3</f>
-        <v>1</v>
-      </c>
-      <c r="C3" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="D3" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -914,7 +916,7 @@
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -927,7 +929,7 @@
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -936,11 +938,13 @@
       </c>
       <c r="B7" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C7" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="D7" s="4" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -953,7 +957,7 @@
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -966,7 +970,7 @@
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -979,7 +983,7 @@
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -992,7 +996,7 @@
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1005,7 +1009,7 @@
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1018,7 +1022,7 @@
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4" t="s">
-        <v>79</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1031,7 +1035,7 @@
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1044,7 +1048,7 @@
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1057,7 +1061,7 @@
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1070,7 +1074,7 @@
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1311,7 +1315,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B36" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1319,12 +1323,12 @@
       </c>
       <c r="C36" s="4"/>
       <c r="D36" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B37" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1332,25 +1336,27 @@
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B38" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C38" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="D38" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B39" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1358,7 +1364,7 @@
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1371,10 +1377,10 @@
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1387,10 +1393,10 @@
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1403,10 +1409,10 @@
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1415,14 +1421,16 @@
       </c>
       <c r="B43" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C43" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>69</v>
+      </c>
       <c r="D43" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E43" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1435,10 +1443,10 @@
       </c>
       <c r="C44" s="4"/>
       <c r="D44" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E44" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F44" s="4"/>
     </row>
@@ -1452,10 +1460,10 @@
       </c>
       <c r="C45" s="4"/>
       <c r="D45" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E45" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -1468,10 +1476,10 @@
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E46" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -1484,7 +1492,7 @@
       </c>
       <c r="C47" s="4"/>
       <c r="D47" s="4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F47"/>
     </row>
@@ -1494,11 +1502,13 @@
       </c>
       <c r="B48" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C48" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>124</v>
+      </c>
       <c r="D48" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F48"/>
     </row>
@@ -1508,11 +1518,11 @@
       </c>
       <c r="B49" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C49" s="4"/>
-      <c r="E49" t="s">
-        <v>69</v>
+      <c r="D49" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="F49"/>
     </row>
@@ -1522,11 +1532,11 @@
       </c>
       <c r="B50" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50" s="4"/>
-      <c r="E50" t="s">
-        <v>68</v>
+      <c r="D50" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="F50"/>
     </row>
@@ -1557,7 +1567,7 @@
         <v>19</v>
       </c>
       <c r="E52" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F52"/>
     </row>
@@ -1567,9 +1577,11 @@
       </c>
       <c r="B53" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C53" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D53" s="4" t="s">
         <v>20</v>
       </c>
@@ -1585,7 +1597,7 @@
       </c>
       <c r="C54" s="4"/>
       <c r="D54" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F54"/>
     </row>
@@ -1595,14 +1607,16 @@
       </c>
       <c r="B55" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C55" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>133</v>
+      </c>
       <c r="D55" s="4" t="s">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="E55" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F55"/>
     </row>
@@ -1612,14 +1626,16 @@
       </c>
       <c r="B56" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C56" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="D56" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E56" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F56"/>
     </row>
@@ -1629,14 +1645,16 @@
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C57" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="D57" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E57" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F57"/>
     </row>
@@ -1650,10 +1668,10 @@
       </c>
       <c r="C58" s="4"/>
       <c r="D58" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E58" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F58"/>
     </row>
@@ -1663,14 +1681,16 @@
       </c>
       <c r="B59" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C59" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="D59" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E59" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F59" s="4"/>
     </row>
@@ -1684,10 +1704,10 @@
       </c>
       <c r="C60" s="4"/>
       <c r="D60" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E60" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -1696,14 +1716,16 @@
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C61" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="D61" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E61" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="F61"/>
     </row>
@@ -1713,14 +1735,16 @@
       </c>
       <c r="B62" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C62" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="D62" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E62" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F62"/>
     </row>
@@ -1730,11 +1754,13 @@
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C63" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="D63" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F63"/>
     </row>
@@ -1744,11 +1770,13 @@
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C64" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="D64" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F64"/>
     </row>
@@ -1758,11 +1786,13 @@
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" ref="B65:B101" si="1">C65&lt;&gt;D65</f>
-        <v>1</v>
-      </c>
-      <c r="C65" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="D65" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E65" s="4"/>
       <c r="F65"/>
@@ -1773,11 +1803,13 @@
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C66" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>64</v>
+      </c>
       <c r="D66" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -1786,11 +1818,13 @@
       </c>
       <c r="B67" s="5" t="b">
         <f>C67&lt;&gt;D67</f>
-        <v>1</v>
-      </c>
-      <c r="C67" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="D67" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -1802,7 +1836,7 @@
         <v>1</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -1811,11 +1845,13 @@
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C69" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="D69" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E69" s="4"/>
     </row>
@@ -1825,11 +1861,13 @@
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C70" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="D70" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F70" s="4"/>
     </row>
@@ -1839,11 +1877,13 @@
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C71" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>72</v>
+      </c>
       <c r="D71" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -1852,11 +1892,13 @@
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C72" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="D72" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -1869,7 +1911,7 @@
       </c>
       <c r="C73" s="4"/>
       <c r="D73" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F73" s="4"/>
     </row>
@@ -1883,7 +1925,7 @@
       </c>
       <c r="C74" s="4"/>
       <c r="D74" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F74" s="4"/>
     </row>
@@ -1893,13 +1935,12 @@
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C75" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="D75" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E75" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1909,17 +1950,19 @@
       </c>
       <c r="B76" s="5" t="b">
         <f>C76&lt;&gt;D76</f>
-        <v>1</v>
-      </c>
-      <c r="C76" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="D76" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E76" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -1928,14 +1971,16 @@
       </c>
       <c r="B77" s="5" t="b">
         <f>C77&lt;&gt;D77</f>
-        <v>1</v>
-      </c>
-      <c r="C77" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="D77" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E77" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F77"/>
     </row>
@@ -1945,14 +1990,16 @@
       </c>
       <c r="B78" s="5" t="b">
         <f>C78&lt;&gt;D78</f>
-        <v>1</v>
-      </c>
-      <c r="C78" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>31</v>
+      </c>
       <c r="D78" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E78" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -1961,14 +2008,16 @@
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C79" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="D79" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E79" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -1981,7 +2030,7 @@
       </c>
       <c r="C80" s="4"/>
       <c r="D80" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -1990,29 +2039,36 @@
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C81" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>108</v>
+      </c>
       <c r="D81" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C82" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="D82" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
+      </c>
+      <c r="E82" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2020,13 +2076,13 @@
       </c>
       <c r="C83" s="4"/>
       <c r="D83" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F83"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2034,27 +2090,29 @@
       </c>
       <c r="C84" s="4"/>
       <c r="D84" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F84" s="4"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C85" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>92</v>
+      </c>
       <c r="D85" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F85" s="4"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2062,13 +2120,13 @@
       </c>
       <c r="C86" s="4"/>
       <c r="D86" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F86"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2076,15 +2134,13 @@
       </c>
       <c r="C87" s="4"/>
       <c r="D87" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>97</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="F87" s="4"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2092,18 +2148,16 @@
       </c>
       <c r="C88" s="4"/>
       <c r="D88" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E88" t="s">
-        <v>48</v>
-      </c>
-      <c r="F88" s="4" t="s">
-        <v>44</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="F88" s="4"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2111,32 +2165,34 @@
       </c>
       <c r="C89" s="4"/>
       <c r="D89" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E89" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F89" s="4"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B90" s="5" t="b">
         <f>C90&lt;&gt;D90</f>
-        <v>1</v>
-      </c>
-      <c r="C90" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="D90" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E90" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2144,30 +2200,35 @@
       </c>
       <c r="C91" s="4"/>
       <c r="D91" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E91" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F91"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>37</v>
+      </c>
+      <c r="B92" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C92" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B92" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C92" s="4"/>
       <c r="D92" t="s">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="E92" t="s">
+        <v>43</v>
       </c>
       <c r="F92"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2175,7 +2236,7 @@
       </c>
       <c r="C93" s="4"/>
       <c r="D93" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F93"/>
     </row>
@@ -2189,10 +2250,10 @@
       </c>
       <c r="C94" s="4"/>
       <c r="D94" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E94" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -2201,14 +2262,16 @@
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C95" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="D95" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E95" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F95"/>
     </row>
@@ -2218,14 +2281,16 @@
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C96" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>83</v>
+      </c>
       <c r="D96" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E96" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F96"/>
     </row>
@@ -2239,10 +2304,10 @@
       </c>
       <c r="C97" s="4"/>
       <c r="D97" s="4" t="s">
-        <v>85</v>
+        <v>131</v>
       </c>
       <c r="E97" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -2255,10 +2320,10 @@
       </c>
       <c r="C98" s="4"/>
       <c r="D98" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E98" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F98"/>
     </row>
@@ -2272,10 +2337,10 @@
       </c>
       <c r="C99" s="4"/>
       <c r="D99" s="4" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="E99" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F99"/>
     </row>
@@ -2292,7 +2357,7 @@
         <v>16</v>
       </c>
       <c r="E100" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -2301,14 +2366,16 @@
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C101" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="D101" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E101" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
